--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484055_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484055_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6381</v>
+        <v>2.1662</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7724</v>
+        <v>4.1602</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1343</v>
+        <v>-1.994</v>
       </c>
       <c r="G2" t="n">
         <v>-2.5692</v>
@@ -610,13 +610,13 @@
         <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8701</v>
+        <v>0.3982</v>
       </c>
       <c r="T2" t="n">
-        <v>1.06</v>
+        <v>0.4478</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1899</v>
+        <v>-0.0496</v>
       </c>
       <c r="V2" t="n">
         <v>2.7502</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2749</v>
+        <v>0.2183</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3242</v>
+        <v>0.8173</v>
       </c>
       <c r="F3" t="n">
         <v>-0.5991</v>
@@ -688,10 +688,10 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.102</v>
+        <v>0.3911</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3683</v>
+        <v>0.1248</v>
       </c>
       <c r="U3" t="n">
         <v>0.2663</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4591</v>
+        <v>-1.0143</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3542</v>
+        <v>1.8271</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8133</v>
+        <v>-2.8414</v>
       </c>
       <c r="G5" t="n">
         <v>-0.06759999999999999</v>
@@ -844,13 +844,13 @@
         <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>1.081</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.0227</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5311</v>
+        <v>0.503</v>
       </c>
       <c r="V5" t="n">
         <v>-1.4724</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.7243</v>
+        <v>-2.8201</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1364</v>
+        <v>2.0967</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.8607</v>
+        <v>-4.9169</v>
       </c>
       <c r="G6" t="n">
         <v>-2.257</v>
@@ -922,13 +922,13 @@
         <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1359</v>
+        <v>1.0402</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9694</v>
+        <v>0.9297</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1666</v>
+        <v>0.1105</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2065</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.334</v>
+        <v>-3.6556</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0219</v>
+        <v>-0.2033</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.312</v>
+        <v>-3.4523</v>
       </c>
       <c r="G7" t="n">
         <v>-3.5223</v>
@@ -1000,13 +1000,13 @@
         <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4029</v>
+        <v>1.0812</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0204</v>
+        <v>0.839</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3825</v>
+        <v>0.2423</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8097</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.9746</v>
+        <v>-3.8904</v>
       </c>
       <c r="E8" t="n">
         <v>-0.9899</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9847</v>
+        <v>-2.9005</v>
       </c>
       <c r="G8" t="n">
         <v>-2.1493</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>0.623</v>
+        <v>0.7071</v>
       </c>
       <c r="T8" t="n">
         <v>0.4025</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2204</v>
+        <v>0.3046</v>
       </c>
       <c r="V8" t="n">
         <v>-0.266</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.2771</v>
+        <v>-4.7287</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6841</v>
+        <v>-1.276</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.593</v>
+        <v>-3.4528</v>
       </c>
       <c r="G9" t="n">
         <v>-4.8521</v>
@@ -1156,13 +1156,13 @@
         <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.5399</v>
       </c>
       <c r="T9" t="n">
-        <v>0.034</v>
+        <v>0.4422</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0425</v>
+        <v>0.0978</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0118</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.2193</v>
+        <v>-7.1405</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4738</v>
+        <v>-1.4512</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.7455</v>
+        <v>-5.6893</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9434</v>
@@ -1234,13 +1234,13 @@
         <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0532</v>
+        <v>0.0255</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1926</v>
+        <v>-0.17</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1394</v>
+        <v>0.1955</v>
       </c>
       <c r="V10" t="n">
         <v>-4.8259</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.113300000000001</v>
+        <v>-7.2299</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5781</v>
+        <v>-2.7789</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.5352</v>
+        <v>-4.4511</v>
       </c>
       <c r="G11" t="n">
         <v>-7.5748</v>
@@ -1312,13 +1312,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1242</v>
+        <v>1.0076</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1021</v>
+        <v>0.9013</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0221</v>
+        <v>0.1062</v>
       </c>
       <c r="V11" t="n">
         <v>-0.266</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.114599999999999</v>
+        <v>-7.8226</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8091</v>
+        <v>-1.2366</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.3055</v>
+        <v>-6.5861</v>
       </c>
       <c r="G12" t="n">
         <v>-1.421</v>
@@ -1390,13 +1390,13 @@
         <v>0.7935</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0227</v>
+        <v>0.2692</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7368</v>
+        <v>-0.1643</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7141</v>
+        <v>0.4335</v>
       </c>
       <c r="V12" t="n">
         <v>-4.4886</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-37.1961</v>
+        <v>-36.2606</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2905000000000006</v>
+        <v>1.225599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-37.4865</v>
+        <v>-37.4867</v>
       </c>
       <c r="G13" t="n">
         <v>-25.6199</v>
@@ -1468,10 +1468,10 @@
         <v>11.9032</v>
       </c>
       <c r="S13" t="n">
-        <v>4.9884</v>
+        <v>5.9234</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7783</v>
+        <v>3.7134</v>
       </c>
       <c r="U13" t="n">
         <v>2.2101</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.5369</v>
+        <v>12.7136</v>
       </c>
       <c r="E14" t="n">
-        <v>11.1239</v>
+        <v>11.532</v>
       </c>
       <c r="F14" t="n">
-        <v>0.413</v>
+        <v>1.1816</v>
       </c>
       <c r="G14" t="n">
         <v>9.3703</v>
@@ -1546,13 +1546,13 @@
         <v>3.1741</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.214</v>
+        <v>-1.0373</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9352</v>
+        <v>-0.5271</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2789</v>
+        <v>-0.5103</v>
       </c>
       <c r="V14" t="n">
         <v>1.2065</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.1026</v>
+        <v>9.6913</v>
       </c>
       <c r="E15" t="n">
-        <v>9.507400000000001</v>
+        <v>8.385</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5953</v>
+        <v>1.3062</v>
       </c>
       <c r="G15" t="n">
         <v>1.6071</v>
@@ -1624,13 +1624,13 @@
         <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4713</v>
+        <v>1.0599</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2924</v>
+        <v>0.1701</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1788</v>
+        <v>0.8898</v>
       </c>
       <c r="V15" t="n">
         <v>6.0323</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.7433</v>
+        <v>7.9092</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1016</v>
+        <v>6.4077</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6418</v>
+        <v>1.5015</v>
       </c>
       <c r="G16" t="n">
         <v>4.4017</v>
@@ -1702,13 +1702,13 @@
         <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0595</v>
+        <v>0.2253</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4988</v>
+        <v>-0.1927</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5582</v>
+        <v>0.418</v>
       </c>
       <c r="V16" t="n">
         <v>3.2821</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6766</v>
+        <v>4.7614</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0794</v>
+        <v>3.2835</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5971</v>
+        <v>1.4779</v>
       </c>
       <c r="G17" t="n">
         <v>2.334</v>
@@ -1780,13 +1780,13 @@
         <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.459</v>
+        <v>-0.3741</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.4194</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8356</v>
+        <v>0.0452</v>
       </c>
       <c r="V17" t="n">
         <v>1.8097</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>V. CASTELLON MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3525</v>
+        <v>3.1018</v>
       </c>
       <c r="E18" t="n">
-        <v>2.272</v>
+        <v>2.7129</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0805</v>
+        <v>0.3888</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1001</v>
+        <v>3.6322</v>
       </c>
       <c r="H18" t="n">
-        <v>1.451</v>
+        <v>1.0734</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6491</v>
+        <v>2.5587</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0036</v>
+        <v>4.7373</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2379</v>
+        <v>2.6061</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7655999999999999</v>
+        <v>2.1311</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9035</v>
+        <v>-1.1051</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7869</v>
+        <v>-1.5327</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1165</v>
+        <v>0.4276</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7935</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R18" t="n">
         <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8071</v>
+        <v>-0.2806</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0056</v>
+        <v>-0.255</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8015</v>
+        <v>-0.0256</v>
       </c>
       <c r="V18" t="n">
-        <v>0.266</v>
+        <v>0.9405</v>
       </c>
       <c r="W18" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. CASTELLON MARTIN</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2192</v>
+        <v>2.6211</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4069</v>
+        <v>2.068</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1876</v>
+        <v>0.5532</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6322</v>
+        <v>2.1001</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0734</v>
+        <v>1.451</v>
       </c>
       <c r="I19" t="n">
-        <v>2.5587</v>
+        <v>0.6491</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7373</v>
+        <v>3.0036</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6061</v>
+        <v>2.2379</v>
       </c>
       <c r="L19" t="n">
-        <v>2.1311</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1051</v>
+        <v>-0.9035</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5327</v>
+        <v>-0.7869</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4276</v>
+        <v>-0.1165</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
         <v>1.7855</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1631</v>
+        <v>-0.5385</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5611</v>
+        <v>-0.2097</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.602</v>
+        <v>-0.3288</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9405</v>
+        <v>0.266</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1123</v>
+        <v>1.1761</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0073</v>
+        <v>0.2114</v>
       </c>
       <c r="F20" t="n">
-        <v>1.105</v>
+        <v>0.9647</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4039</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3486</v>
+        <v>-0.2849</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4988</v>
+        <v>-0.2947</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1501</v>
+        <v>0.0098</v>
       </c>
       <c r="V20" t="n">
         <v>0.6745</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0179</v>
+        <v>0.1718</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1694</v>
+        <v>2.8633</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1515</v>
+        <v>-2.6915</v>
       </c>
       <c r="G21" t="n">
         <v>0.5907</v>
@@ -2092,13 +2092,13 @@
         <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3557</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1191</v>
+        <v>-0.187</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6287</v>
+        <v>-0.1687</v>
       </c>
       <c r="V21" t="n">
         <v>0.532</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5654</v>
+        <v>-2.2295</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1813</v>
+        <v>0.0228</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3841</v>
+        <v>-2.2523</v>
       </c>
       <c r="G22" t="n">
         <v>1.9877</v>
@@ -2170,13 +2170,13 @@
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0175</v>
+        <v>-0.6816</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4988</v>
+        <v>-0.2947</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5187</v>
+        <v>-0.3869</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1469</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>37.1959</v>
+        <v>39.91679999999999</v>
       </c>
       <c r="E23" t="n">
         <v>37.4866</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2905000000000006</v>
+        <v>2.4301</v>
       </c>
       <c r="G23" t="n">
         <v>25.6199</v>
@@ -2248,13 +2248,13 @@
         <v>15.8707</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.988100000000001</v>
+        <v>-2.2675</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.2103</v>
+        <v>-2.2102</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.7783</v>
+        <v>-0.0575</v>
       </c>
       <c r="V23" t="n">
         <v>12.5967</v>
